--- a/efficiency_profit_dev_request.xlsx
+++ b/efficiency_profit_dev_request.xlsx
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F155"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -676,12 +676,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>요청 대상</t>
+          <t>대상 시스템</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>개발팀</t>
+          <t>사업건전성 대시보드</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>v0.2</t>
+          <t>v0.3</t>
         </is>
       </c>
       <c r="C5" s="6" t="n"/>
@@ -712,14 +712,14 @@
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>솔루션사업부는 12개 상품의 사업 건전성을 체계적으로 관리하기 위해 사업건전성 대시보드를 구축하고 있습니다. 그 중 효율/수익 영역은 고객 1인당 수익성, 고객 획득 비용 효율, 매출 및 수익성 추이를 한눈에 파악하기 위한 핵심 영역입니다.</t>
+          <t>사업건전성 대시보드의 효율/수익 영역 지표 산출 로직을 드리니, 화면 개발을 요청합니다.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>원천 데이터(vf219, vf599 등)는 당사 DB에 이미 수신 중이며, 해당 데이터를 기반으로 지표 산출 로직 개발 및 대시보드 화면 개발을 요청합니다.</t>
+          <t>원천 데이터(vf219, vf599 등)는 당사 DB에 이미 수신 중이며, Row 1~6 화면은 Tableau로 기 구현되어 있어 본 요청서의 개발 범위에서 제외합니다.</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>LTV · CAC · LTV:CAC Ratio · CAC Payback · ARPA 등 지표별 산출 기준에 따른 계산 로직 구현</t>
+          <t>LTV · CAC · LTV:CAC Ratio · CAC Payback 지표별 산출 기준에 따른 계산 로직 구현</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
@@ -795,12 +795,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>화면 개발</t>
+          <t>마스터 데이터</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>효율/수익 페이지 — 6 Row × 12 카드 구성의 대시보드 화면 개발</t>
+          <t>상품 필터용 상품 목록 제공 요청</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -816,2109 +816,2074 @@
       <c r="F14" s="11" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Tableau 기 구현 — 본 요청 범위 제외 (와이어프레임 별도 제공 예정)</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>※ 납기 일정은 협의 후 확정 예정입니다.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="6" customHeight="1"/>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="17" ht="6" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>3. 원천 데이터 현황</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>아래 데이터는 당사 DB에 이미 수신 중이며, 별도 인터페이스 요청 없이 사용 가능합니다.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>필드/테이블</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>조회 조건</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>히스토리 범위</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>활용 지표</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>vf219</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>매출총계 (상품별 연도별)</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>상품 코드 · 연도 기준 컬럼 — 개발팀 확인 필요</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>2022년 ~ 현재</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>LTV · ARPA · 이탈률</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>vf599</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>영업/마케팅 비용 (상품별 연도별)</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>상품 코드 · 연도 기준 컬럼 — 개발팀 확인 필요</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>2022년 ~ 현재</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>CAC</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>Revenue · Operating Profit · Plan · FTE · ARR 등</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>개발팀 확인 필요</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>Row 5 기준: 2023.10 ~ 현재</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>Row 1·3·4·5·6 지표</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>※ vf219는 RC/NRC 데이터 분리가 어려우므로, 실무 적용 시 전체 매출을 Recurring Revenue로 간주하여 사용합니다.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="6" customHeight="1"/>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="25" ht="6" customHeight="1"/>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>4. 마스터 데이터 요청 (화면 필터용)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>화면 상단 상품 드롭다운 필터 구현을 위해 아래 마스터 데이터가 필요합니다.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>샘플값</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr"/>
-      <c r="F27" s="9" t="inlineStr"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr"/>
+      <c r="F28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>상품 목록</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>필터 드롭다운에 표시될 상품명 목록 (코드 + 표시명)</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>ZTM · Nexprime SCM · Knox Portal · EMS 등 13개</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr"/>
-      <c r="F28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr"/>
+      <c r="F29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>상품 그룹핑</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>상품 개별 / 전체(All) 선택 구분</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>Knox (All) = Knox Portal + Knox Meeting + Knox EFSS/Drive</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr"/>
-      <c r="F29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr"/>
+      <c r="F30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>EMS 예외 처리</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>EMS / EMS(All) 선택 시 LTV:CAC 관련 카드 N/A 표시 처리용 플래그</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>is_ltv_applicable: Y/N</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr"/>
-      <c r="F30" s="10" t="inlineStr"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr"/>
+      <c r="F31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>※ 상품 코드 체계 및 마스터 테이블명은 개발팀 확인 후 공유 바랍니다.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="6" customHeight="1"/>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="33" ht="6" customHeight="1"/>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>5. 상품 분류 및 지표 산출 가능 여부</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>상품</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>License Type</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>Price Type</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>RC/NRC</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>LTV / CAC / LTV:CAC / CAC Payback</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>ZTM</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>✅ / ✅ / ✅ / ✅</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Nexprime SCM</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>✅ / ✅ / ✅ / ✅</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr"/>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>Nexprime SCM Mobile</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>✅ / ✅ / ✅ / ✅</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr"/>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Nexprime SCM (All)</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>✅ / ✅ / ✅ / ✅</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Nexprime HCM</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>✅ / ✅ / ✅ / ✅</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr"/>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Knox Portal</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>Usage</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>✅ / ✅ / ✅ / ✅</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>Knox Meeting</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>Usage</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>✅ / ✅ / ✅ / ✅</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr"/>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>Knox EFSS/Drive</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>Usage</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D43" s="11" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>✅ / ✅ / ✅ / ✅</t>
         </is>
       </c>
-      <c r="F42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>Knox (All)</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>Usage</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr">
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>✅ / ✅ / ✅ / ✅</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr"/>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>EMM Cloud</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>Usage</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D45" s="11" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>✅ / ✅ / ✅ / ✅</t>
         </is>
       </c>
-      <c r="F44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>Brity Automation</t>
         </is>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>Term+Perpetual</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>Fixed+One-time</t>
         </is>
       </c>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>RC+Non-RC</t>
         </is>
       </c>
-      <c r="E45" s="10" t="inlineStr">
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>✅ / ✅ / ✅ / ✅</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr"/>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>EMS</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>Term+Perpetual</t>
         </is>
       </c>
-      <c r="C46" s="11" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>Fixed+One-time</t>
         </is>
       </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>RC+Non-RC</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>❌ / ✅ / ❌ / ❌</t>
         </is>
       </c>
-      <c r="F46" s="11" t="inlineStr"/>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>EMS (All)</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>Term+Perpetual</t>
         </is>
       </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>Fixed+One-time</t>
         </is>
       </c>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>RC+Non-RC</t>
         </is>
       </c>
-      <c r="E47" s="10" t="inlineStr">
+      <c r="E48" s="10" t="inlineStr">
         <is>
           <t>❌ / ✅ / ❌ / ❌</t>
         </is>
       </c>
-      <c r="F47" s="10" t="inlineStr"/>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="F48" s="10" t="inlineStr"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>※ EMS / EMS (All): Recurring 비중 약 9% (라이선스+운영 149억 / 전체 1,572억), 데이터 분리 불가로 LTV · LTV:CAC · CAC Payback 산출 제외. CAC만 산출.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="6" customHeight="1"/>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+    <row r="50" ht="6" customHeight="1"/>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>6. 지표별 산출 기준</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="14" t="inlineStr">
-        <is>
-          <t>6-1. ARPA (Average Revenue Per Account)</t>
-        </is>
-      </c>
-    </row>
     <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>6-1. LTV (Customer Lifetime Value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr"/>
-      <c r="D52" s="9" t="inlineStr"/>
-      <c r="E52" s="9" t="inlineStr"/>
-      <c r="F52" s="9" t="inlineStr"/>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>산식</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>sum(vf219) ÷ 고객 수</t>
-        </is>
-      </c>
+      <c r="C53" s="9" t="inlineStr"/>
+      <c r="D53" s="9" t="inlineStr"/>
+      <c r="E53" s="9" t="inlineStr"/>
+      <c r="F53" s="9" t="inlineStr"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>고객 수 기준</t>
-        </is>
-      </c>
-      <c r="B54" s="11" t="inlineStr">
-        <is>
-          <t>해당 연도 vf219 ≠ 0인 고객 수</t>
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>산식 (이론)</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>(Recurring 매출에 대한 ARPA ÷ 이탈률) + (연 일회성 매출 ÷ 고객 수)</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>Revenue 범위</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>vf219 전체 (RC/NRC 분리 불가로 전체를 Recurring으로 간주)</t>
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>실무 적용 산식</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>(sum(vf219) ÷ 고객 수 ÷ 이탈률) + (연 일회성 매출 ÷ 고객 수)</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>RC/NRC 데이터 분리 불가로 vf219 전체를 Recurring으로 간주</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>적용 상품</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>EMS / EMS(All) 제외 전 상품</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>표시 주기</t>
         </is>
       </c>
-      <c r="B56" s="11" t="inlineStr">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>Yearly (2023 / 2024 / 2025)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="14" t="inlineStr">
-        <is>
-          <t>6-2. 이탈률 (Churn Rate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="9" t="inlineStr">
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └ 구성 요소: ARPA / 이탈률</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr"/>
-      <c r="D58" s="9" t="inlineStr"/>
-      <c r="E58" s="9" t="inlineStr"/>
-      <c r="F58" s="9" t="inlineStr"/>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>산식</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t>(1 - (N-1년 sum(vf219) ÷ N-2년 sum(vf219))) × 100</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="B60" s="11" t="inlineStr">
-        <is>
-          <t>N-1년 ≥ N-2년이면 이탈률 = 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>이탈률 = 0일 때</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="inlineStr">
-        <is>
-          <t>LTV · LTV:CAC · CAC Payback 모두 빈칸 표시</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="14" t="inlineStr">
-        <is>
-          <t>6-3. LTV (Customer Lifetime Value)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="9" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr"/>
+      <c r="D61" s="9" t="inlineStr"/>
+      <c r="E61" s="9" t="inlineStr"/>
+      <c r="F61" s="9" t="inlineStr"/>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>ARPA 산식</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>sum(vf219) ÷ 고객 수  (해당 연도 vf219 ≠ 0인 고객 수 기준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>이탈률 산식</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>(1 - (N-1년 sum(vf219) ÷ N-2년 sum(vf219))) × 100  ※ N-1년 ≥ N-2년이면 0 → LTV 빈칸</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>6-2. CAC (Customer Acquisition Cost)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr"/>
-      <c r="D63" s="9" t="inlineStr"/>
-      <c r="E63" s="9" t="inlineStr"/>
-      <c r="F63" s="9" t="inlineStr"/>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>산식</t>
-        </is>
-      </c>
-      <c r="B64" s="10" t="inlineStr">
-        <is>
-          <t>ARPA ÷ 이탈률</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t>적용 상품</t>
-        </is>
-      </c>
-      <c r="B65" s="11" t="inlineStr">
-        <is>
-          <t>EMS / EMS(All) 제외 전 상품</t>
-        </is>
-      </c>
+      <c r="C65" s="9" t="inlineStr"/>
+      <c r="D65" s="9" t="inlineStr"/>
+      <c r="E65" s="9" t="inlineStr"/>
+      <c r="F65" s="9" t="inlineStr"/>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>표시 주기</t>
+          <t>산식</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Yearly (2023 / 2024 / 2025)</t>
+          <t>N-2년 sum(vf599) ÷ N-1년 신규 고객 수</t>
         </is>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>신규 고객 정의</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>억원</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="14" t="inlineStr">
-        <is>
-          <t>6-4. CAC (Customer Acquisition Cost)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t>내용</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr"/>
-      <c r="D69" s="9" t="inlineStr"/>
-      <c r="E69" s="9" t="inlineStr"/>
-      <c r="F69" s="9" t="inlineStr"/>
+          <t>N-2년 vf219 = 0 AND N-1년 vf219 ≠ 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>적용 상품</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>전체 (EMS 포함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>표시 주기</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>Yearly (2023 / 2024 / 2025)</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>산식</t>
+          <t>단위</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>N-2년 sum(vf599) ÷ N-1년 신규 고객 수</t>
+          <t>억원</t>
         </is>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>신규 고객 정의</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>N-2년 vf219 = 0 AND N-1년 vf219 ≠ 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="10" t="inlineStr">
-        <is>
-          <t>적용 상품</t>
-        </is>
-      </c>
-      <c r="B72" s="10" t="inlineStr">
-        <is>
-          <t>전체 (EMS 포함)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="11" t="inlineStr">
-        <is>
-          <t>표시 주기</t>
-        </is>
-      </c>
-      <c r="B73" s="11" t="inlineStr">
-        <is>
-          <t>Yearly (2023 / 2024 / 2025)</t>
-        </is>
-      </c>
+          <t>신규 고객 수 = 0이면 빈칸</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>6-3. LTV:CAC Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr"/>
+      <c r="D73" s="9" t="inlineStr"/>
+      <c r="E73" s="9" t="inlineStr"/>
+      <c r="F73" s="9" t="inlineStr"/>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>산식</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>억원</t>
+          <t>LTV ÷ CAC</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>적용 상품</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>신규 고객 수 = 0이면 빈칸</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="14" t="inlineStr">
-        <is>
-          <t>6-5. LTV:CAC Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="9" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B77" s="9" t="inlineStr">
-        <is>
-          <t>내용</t>
-        </is>
-      </c>
-      <c r="C77" s="9" t="inlineStr"/>
-      <c r="D77" s="9" t="inlineStr"/>
-      <c r="E77" s="9" t="inlineStr"/>
-      <c r="F77" s="9" t="inlineStr"/>
+          <t>EMS / EMS(All) 제외 전 상품</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>배수 (예: 1.6배)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>참고 기준</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>LTV : CAC = 3 : 1이 적정 수준</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="10" t="inlineStr">
         <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>LTV 또는 CAC 빈칸이면 빈칸</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>6-4. CAC Payback Period</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr"/>
+      <c r="E80" s="9" t="inlineStr"/>
+      <c r="F80" s="9" t="inlineStr"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
           <t>산식</t>
         </is>
       </c>
-      <c r="B78" s="10" t="inlineStr">
-        <is>
-          <t>LTV ÷ CAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>(CAC ÷ ARPA) × 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
         <is>
           <t>적용 상품</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>EMS / EMS(All) 제외 전 상품</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="10" t="inlineStr">
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="B80" s="10" t="inlineStr">
-        <is>
-          <t>배수 (예: 1.6배)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="11" t="inlineStr">
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>개월</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>참고 기준</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
-        <is>
-          <t>LTV : CAC = 3 : 1이 적정 수준</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="10" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="B82" s="10" t="inlineStr">
-        <is>
-          <t>LTV 또는 CAC 빈칸이면 빈칸</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="14" t="inlineStr">
-        <is>
-          <t>6-6. CAC Payback Period</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="9" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>내용</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr"/>
-      <c r="D84" s="9" t="inlineStr"/>
-      <c r="E84" s="9" t="inlineStr"/>
-      <c r="F84" s="9" t="inlineStr"/>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>B2B SaaS 적정 수준: 12개월 이하</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>산식</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>(CAC ÷ ARPA) × 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="11" t="inlineStr">
-        <is>
-          <t>적용 상품</t>
-        </is>
-      </c>
-      <c r="B86" s="11" t="inlineStr">
-        <is>
-          <t>EMS / EMS(All) 제외 전 상품</t>
+          <t>ARPA = 0 또는 CAC 빈칸이면 빈칸</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>6-7. Row 1 · 3 · 4 · 5 · 6 지표 (산식 확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="10" t="inlineStr">
-        <is>
-          <t>단위</t>
-        </is>
-      </c>
-      <c r="B87" s="10" t="inlineStr">
-        <is>
-          <t>개월</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="11" t="inlineStr">
-        <is>
-          <t>참고 기준</t>
-        </is>
-      </c>
-      <c r="B88" s="11" t="inlineStr">
-        <is>
-          <t>B2B SaaS 적정 수준: 12개월 이하</t>
-        </is>
-      </c>
+      <c r="A87" s="15" t="inlineStr">
+        <is>
+          <t>※ 아래 지표는 사내 기존 BI 시스템에서 이미 산출 중입니다. 개발팀은 기존 산출 로직 및 데이터 출처(테이블/필드명)를 확인하여 동일 기준으로 적용하되, 확인된 산식을 기획팀에 공유 바랍니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>지표명</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr"/>
+      <c r="E88" s="9" t="inlineStr"/>
+      <c r="F88" s="9" t="inlineStr"/>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>ARPA = 0 또는 CAC 빈칸이면 빈칸</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="14" t="inlineStr">
-        <is>
-          <t>6-7. Row 1 · 3 · 4 · 5 · 6 지표 (산식 확인 필요)</t>
-        </is>
-      </c>
+          <t>Gross Sales Efficiency / Net Sales Efficiency</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>기존 BI 로직 적용</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr"/>
+      <c r="E89" s="10" t="inlineStr"/>
+      <c r="F89" s="10" t="inlineStr"/>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t>Row 3</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>ARPA by ACV / ARPA by MRR (분기별)</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>기존 BI 로직 적용</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr"/>
+      <c r="E90" s="11" t="inlineStr"/>
+      <c r="F90" s="11" t="inlineStr"/>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="15" t="inlineStr">
-        <is>
-          <t>※ 아래 지표는 사내 기존 BI 시스템에서 이미 산출 중입니다. 개발팀은 기존 산출 로직 및 데이터 출처(테이블/필드명)를 확인하여 동일 기준으로 적용하되, 확인된 산식을 기획팀에 공유 바랍니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="9" t="inlineStr">
-        <is>
-          <t>Row</t>
-        </is>
-      </c>
-      <c r="B92" s="9" t="inlineStr">
-        <is>
-          <t>지표명</t>
-        </is>
-      </c>
-      <c r="C92" s="9" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="D92" s="9" t="inlineStr"/>
-      <c r="E92" s="9" t="inlineStr"/>
-      <c r="F92" s="9" t="inlineStr"/>
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>Row 4</t>
+        </is>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>Revenue on FTE / Rule of 40</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>기존 BI 로직 적용 — FTE 데이터 출처 확인 필요</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr"/>
+      <c r="E91" s="10" t="inlineStr"/>
+      <c r="F91" s="10" t="inlineStr"/>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t>Row 5</t>
+        </is>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>Revenue &amp; Operating Profit / % Gross Margin &amp; Operating Profit</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>기존 BI 로직 적용</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr"/>
+      <c r="E92" s="11" t="inlineStr"/>
+      <c r="F92" s="11" t="inlineStr"/>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>Row 1</t>
+          <t>Row 6</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>Gross Sales Efficiency / Net Sales Efficiency</t>
+          <t>Revenue vs. Plan / Operating Profit vs. Plan</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>기존 BI 로직 적용</t>
+          <t>기존 BI 로직 적용 — Plan 데이터 출처 확인 필요</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr"/>
       <c r="E93" s="10" t="inlineStr"/>
       <c r="F93" s="10" t="inlineStr"/>
     </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="11" t="inlineStr">
-        <is>
-          <t>Row 3</t>
-        </is>
-      </c>
-      <c r="B94" s="11" t="inlineStr">
-        <is>
-          <t>ARPA by ACV / ARPA by MRR (분기별)</t>
-        </is>
-      </c>
-      <c r="C94" s="11" t="inlineStr">
-        <is>
-          <t>기존 BI 로직 적용</t>
-        </is>
-      </c>
-      <c r="D94" s="11" t="inlineStr"/>
-      <c r="E94" s="11" t="inlineStr"/>
-      <c r="F94" s="11" t="inlineStr"/>
-    </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="10" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B95" s="10" t="inlineStr">
-        <is>
-          <t>Revenue on FTE / Rule of 40</t>
-        </is>
-      </c>
-      <c r="C95" s="10" t="inlineStr">
-        <is>
-          <t>기존 BI 로직 적용 — FTE 데이터 출처 확인 필요</t>
-        </is>
-      </c>
-      <c r="D95" s="10" t="inlineStr"/>
-      <c r="E95" s="10" t="inlineStr"/>
-      <c r="F95" s="10" t="inlineStr"/>
-    </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="11" t="inlineStr">
-        <is>
-          <t>Row 5</t>
-        </is>
-      </c>
-      <c r="B96" s="11" t="inlineStr">
-        <is>
-          <t>Revenue &amp; Operating Profit / % Gross Margin &amp; Operating Profit</t>
-        </is>
-      </c>
-      <c r="C96" s="11" t="inlineStr">
-        <is>
-          <t>기존 BI 로직 적용</t>
-        </is>
-      </c>
-      <c r="D96" s="11" t="inlineStr"/>
-      <c r="E96" s="11" t="inlineStr"/>
-      <c r="F96" s="11" t="inlineStr"/>
+    <row r="94" ht="6" customHeight="1"/>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>7. 예외 처리 기준 (공통)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>조건</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>처리 방식</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>영향 지표</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr"/>
+      <c r="E96" s="9" t="inlineStr"/>
+      <c r="F96" s="9" t="inlineStr"/>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>Row 6</t>
+          <t>이탈률 = 0</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>Revenue vs. Plan / Operating Profit vs. Plan</t>
+          <t>빈칸 표시</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>기존 BI 로직 적용 — Plan 데이터 출처 확인 필요</t>
+          <t>LTV · LTV:CAC · CAC Payback</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr"/>
       <c r="E97" s="10" t="inlineStr"/>
       <c r="F97" s="10" t="inlineStr"/>
     </row>
-    <row r="98" ht="6" customHeight="1"/>
-    <row r="99" ht="22" customHeight="1">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
-          <t>7. 예외 처리 기준 (공통)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>조건</t>
-        </is>
-      </c>
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t>처리 방식</t>
-        </is>
-      </c>
-      <c r="C100" s="9" t="inlineStr">
-        <is>
-          <t>영향 지표</t>
-        </is>
-      </c>
-      <c r="D100" s="9" t="inlineStr"/>
-      <c r="E100" s="9" t="inlineStr"/>
-      <c r="F100" s="9" t="inlineStr"/>
-    </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="10" t="inlineStr">
-        <is>
-          <t>이탈률 = 0</t>
-        </is>
-      </c>
-      <c r="B101" s="10" t="inlineStr">
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>신규 고객 수 = 0</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
         <is>
           <t>빈칸 표시</t>
         </is>
       </c>
-      <c r="C101" s="10" t="inlineStr">
-        <is>
-          <t>LTV · LTV:CAC · CAC Payback</t>
-        </is>
-      </c>
-      <c r="D101" s="10" t="inlineStr"/>
-      <c r="E101" s="10" t="inlineStr"/>
-      <c r="F101" s="10" t="inlineStr"/>
-    </row>
-    <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="11" t="inlineStr">
-        <is>
-          <t>신규 고객 수 = 0</t>
-        </is>
-      </c>
-      <c r="B102" s="11" t="inlineStr">
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>CAC · LTV:CAC · CAC Payback</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr"/>
+      <c r="E98" s="11" t="inlineStr"/>
+      <c r="F98" s="11" t="inlineStr"/>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>ARPA = 0</t>
+        </is>
+      </c>
+      <c r="B99" s="10" t="inlineStr">
         <is>
           <t>빈칸 표시</t>
         </is>
       </c>
-      <c r="C102" s="11" t="inlineStr">
-        <is>
-          <t>CAC · LTV:CAC · CAC Payback</t>
-        </is>
-      </c>
-      <c r="D102" s="11" t="inlineStr"/>
-      <c r="E102" s="11" t="inlineStr"/>
-      <c r="F102" s="11" t="inlineStr"/>
-    </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="10" t="inlineStr">
-        <is>
-          <t>ARPA = 0</t>
-        </is>
-      </c>
-      <c r="B103" s="10" t="inlineStr">
-        <is>
-          <t>빈칸 표시</t>
-        </is>
-      </c>
-      <c r="C103" s="10" t="inlineStr">
+      <c r="C99" s="10" t="inlineStr">
         <is>
           <t>CAC Payback</t>
         </is>
       </c>
-      <c r="D103" s="10" t="inlineStr"/>
-      <c r="E103" s="10" t="inlineStr"/>
-      <c r="F103" s="10" t="inlineStr"/>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="11" t="inlineStr">
+      <c r="D99" s="10" t="inlineStr"/>
+      <c r="E99" s="10" t="inlineStr"/>
+      <c r="F99" s="10" t="inlineStr"/>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
         <is>
           <t>EMS / EMS(All) 선택 시</t>
         </is>
       </c>
-      <c r="B104" s="11" t="inlineStr">
+      <c r="B100" s="11" t="inlineStr">
         <is>
           <t>LTV · LTV:CAC · CAC Payback 카드 N/A 표시</t>
         </is>
       </c>
-      <c r="C104" s="11" t="inlineStr">
+      <c r="C100" s="11" t="inlineStr">
         <is>
           <t>Row 2 전체</t>
         </is>
       </c>
-      <c r="D104" s="11" t="inlineStr"/>
-      <c r="E104" s="11" t="inlineStr"/>
-      <c r="F104" s="11" t="inlineStr"/>
-    </row>
-    <row r="105" ht="6" customHeight="1"/>
-    <row r="106" ht="22" customHeight="1">
-      <c r="A106" s="7" t="inlineStr">
+      <c r="D100" s="11" t="inlineStr"/>
+      <c r="E100" s="11" t="inlineStr"/>
+      <c r="F100" s="11" t="inlineStr"/>
+    </row>
+    <row r="101" ht="6" customHeight="1"/>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="7" t="inlineStr">
         <is>
           <t>8. 화면 개발 스펙</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="14" t="inlineStr">
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="14" t="inlineStr">
         <is>
           <t>8-1. 전체 레이아웃</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="9" t="inlineStr">
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="9" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B108" s="9" t="inlineStr">
+      <c r="B104" s="9" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="C108" s="9" t="inlineStr"/>
-      <c r="D108" s="9" t="inlineStr"/>
-      <c r="E108" s="9" t="inlineStr"/>
-      <c r="F108" s="9" t="inlineStr"/>
+      <c r="C104" s="9" t="inlineStr"/>
+      <c r="D104" s="9" t="inlineStr"/>
+      <c r="E104" s="9" t="inlineStr"/>
+      <c r="F104" s="9" t="inlineStr"/>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>6 Row × 2 카드 (총 12 카드)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>상단 필터</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>상품 드롭다운 (전체 / 상품별 선택) — Section 4 마스터 데이터 기반</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>표시 주기</t>
+        </is>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>Yearly 기본 (Row 3·4·5·6은 분기/월별)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>페이지 배경</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>#F5F5F5</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>구성</t>
+          <t>카드 스타일</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>6 Row × 2 카드 (총 12 카드)</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="11" t="inlineStr">
-        <is>
-          <t>상단 필터</t>
-        </is>
-      </c>
-      <c r="B110" s="11" t="inlineStr">
-        <is>
-          <t>상품 드롭다운 (전체 / 상품별 선택) — Section 4 마스터 데이터 기반</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="10" t="inlineStr">
-        <is>
-          <t>표시 주기</t>
-        </is>
-      </c>
-      <c r="B111" s="10" t="inlineStr">
-        <is>
-          <t>Yearly 기본 (Row 3·4·5·6은 분기/월별)</t>
+          <t>border-radius: 8px · box-shadow: 0 2px 8px rgba(0,0,0,0.08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="14" t="inlineStr">
+        <is>
+          <t>8-2. Row별 카드 스펙</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>카드 (좌)</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>카드 (우)</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>차트 타입</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>X축</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>단위</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="11" t="inlineStr">
-        <is>
-          <t>페이지 배경</t>
-        </is>
-      </c>
-      <c r="B112" s="11" t="inlineStr">
-        <is>
-          <t>#F5F5F5</t>
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>Row 1</t>
+        </is>
+      </c>
+      <c r="B112" s="10" t="inlineStr">
+        <is>
+          <t>Gross Sales Efficiency</t>
+        </is>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
+        <is>
+          <t>Net Sales Efficiency</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="inlineStr">
+        <is>
+          <t>단색 바 차트</t>
+        </is>
+      </c>
+      <c r="E112" s="10" t="inlineStr">
+        <is>
+          <t>2022 / 2023 / 2024</t>
+        </is>
+      </c>
+      <c r="F112" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="10" t="inlineStr">
-        <is>
-          <t>카드 스타일</t>
-        </is>
-      </c>
-      <c r="B113" s="10" t="inlineStr">
-        <is>
-          <t>border-radius: 8px · box-shadow: 0 2px 8px rgba(0,0,0,0.08)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="14" t="inlineStr">
-        <is>
-          <t>8-2. Row별 카드 스펙</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="9" t="inlineStr">
-        <is>
-          <t>Row</t>
-        </is>
-      </c>
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t>카드 (좌)</t>
-        </is>
-      </c>
-      <c r="C115" s="9" t="inlineStr">
-        <is>
-          <t>카드 (우)</t>
-        </is>
-      </c>
-      <c r="D115" s="9" t="inlineStr">
-        <is>
-          <t>차트 타입</t>
-        </is>
-      </c>
-      <c r="E115" s="9" t="inlineStr">
-        <is>
-          <t>X축</t>
-        </is>
-      </c>
-      <c r="F115" s="9" t="inlineStr">
-        <is>
-          <t>단위</t>
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>Row 2</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>CAC / LTV / LTV:CAC Ratio</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>CAC Payback Period</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>콤비네이션(좌) · 라인(우)</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>2022 / 2023 / 2024</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>억원 · 배수 / 개월</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>Row 3</t>
+        </is>
+      </c>
+      <c r="B114" s="10" t="inlineStr">
+        <is>
+          <t>ARPA by ACV</t>
+        </is>
+      </c>
+      <c r="C114" s="10" t="inlineStr">
+        <is>
+          <t>ARPA by MRR</t>
+        </is>
+      </c>
+      <c r="D114" s="10" t="inlineStr">
+        <is>
+          <t>다중 라인 차트</t>
+        </is>
+      </c>
+      <c r="E114" s="10" t="inlineStr">
+        <is>
+          <t>22.4Q ~ 25.3Q (12분기)</t>
+        </is>
+      </c>
+      <c r="F114" s="10" t="inlineStr">
+        <is>
+          <t>억원 / 천만원</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>Row 4</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>Revenue on FTE</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>Rule of 40</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>라인(좌) · 다중 라인(우)</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>반기 / 22.4Q ~ 25.3Q</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>억원 / %</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>Row 1</t>
+          <t>Row 5</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>Gross Sales Efficiency</t>
+          <t>Revenue &amp; Operating Profit</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Net Sales Efficiency</t>
+          <t>% Gross Margin &amp; Operating Profit</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>단색 바 차트</t>
+          <t>콤비네이션 · 다중 라인</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
         <is>
-          <t>2022 / 2023 / 2024</t>
+          <t>월별 (23.10 ~ 25.10)</t>
         </is>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>억원 / %</t>
         </is>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>Row 2</t>
+          <t>Row 6</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>CAC / LTV / LTV:CAC Ratio</t>
+          <t>Revenue vs. Plan</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>CAC Payback Period</t>
+          <t>Operating Profit vs. Plan</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>콤비네이션(좌) · 라인(우)</t>
+          <t>트리플 바 + 달성률 라인</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>2022 / 2023 / 2024</t>
+          <t>월별 (1월 ~ 7월)</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
-          <t>억원 · 배수 / 개월</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="10" t="inlineStr">
-        <is>
-          <t>Row 3</t>
-        </is>
-      </c>
-      <c r="B118" s="10" t="inlineStr">
-        <is>
-          <t>ARPA by ACV</t>
-        </is>
-      </c>
-      <c r="C118" s="10" t="inlineStr">
-        <is>
-          <t>ARPA by MRR</t>
-        </is>
-      </c>
-      <c r="D118" s="10" t="inlineStr">
-        <is>
-          <t>다중 라인 차트</t>
-        </is>
-      </c>
-      <c r="E118" s="10" t="inlineStr">
-        <is>
-          <t>22.4Q ~ 25.3Q (12분기)</t>
-        </is>
-      </c>
-      <c r="F118" s="10" t="inlineStr">
-        <is>
-          <t>억원 / 천만원</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="11" t="inlineStr">
-        <is>
-          <t>Row 4</t>
-        </is>
-      </c>
-      <c r="B119" s="11" t="inlineStr">
-        <is>
-          <t>Revenue on FTE</t>
-        </is>
-      </c>
-      <c r="C119" s="11" t="inlineStr">
-        <is>
-          <t>Rule of 40</t>
-        </is>
-      </c>
-      <c r="D119" s="11" t="inlineStr">
-        <is>
-          <t>라인(좌) · 다중 라인(우)</t>
-        </is>
-      </c>
-      <c r="E119" s="11" t="inlineStr">
-        <is>
-          <t>반기 / 22.4Q ~ 25.3Q</t>
-        </is>
-      </c>
-      <c r="F119" s="11" t="inlineStr">
-        <is>
           <t>억원 / %</t>
         </is>
       </c>
     </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="14" t="inlineStr">
+        <is>
+          <t>8-3. 색상 시스템</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>요소</t>
+        </is>
+      </c>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>색상 코드</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="inlineStr"/>
+      <c r="D119" s="9" t="inlineStr"/>
+      <c r="E119" s="9" t="inlineStr"/>
+      <c r="F119" s="9" t="inlineStr"/>
+    </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="10" t="inlineStr">
-        <is>
-          <t>Row 5</t>
-        </is>
-      </c>
-      <c r="B120" s="10" t="inlineStr">
-        <is>
-          <t>Revenue &amp; Operating Profit</t>
-        </is>
-      </c>
-      <c r="C120" s="10" t="inlineStr">
-        <is>
-          <t>% Gross Margin &amp; Operating Profit</t>
-        </is>
-      </c>
-      <c r="D120" s="10" t="inlineStr">
-        <is>
-          <t>콤비네이션 · 다중 라인</t>
-        </is>
-      </c>
-      <c r="E120" s="10" t="inlineStr">
-        <is>
-          <t>월별 (23.10 ~ 25.10)</t>
-        </is>
-      </c>
-      <c r="F120" s="10" t="inlineStr">
-        <is>
-          <t>억원 / %</t>
+      <c r="A120" s="16" t="inlineStr">
+        <is>
+          <t>주요 바 차트 (라이트 블루)</t>
+        </is>
+      </c>
+      <c r="B120" s="17" t="inlineStr">
+        <is>
+          <t>#90CAF9</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="11" t="inlineStr">
-        <is>
-          <t>Row 6</t>
-        </is>
-      </c>
-      <c r="B121" s="11" t="inlineStr">
-        <is>
-          <t>Revenue vs. Plan</t>
-        </is>
-      </c>
-      <c r="C121" s="11" t="inlineStr">
-        <is>
-          <t>Operating Profit vs. Plan</t>
-        </is>
-      </c>
-      <c r="D121" s="11" t="inlineStr">
-        <is>
-          <t>트리플 바 + 달성률 라인</t>
-        </is>
-      </c>
-      <c r="E121" s="11" t="inlineStr">
-        <is>
-          <t>월별 (1월 ~ 7월)</t>
-        </is>
-      </c>
-      <c r="F121" s="11" t="inlineStr">
-        <is>
-          <t>억원 / %</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="14" t="inlineStr">
-        <is>
-          <t>8-3. 색상 시스템</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="9" t="inlineStr">
-        <is>
-          <t>요소</t>
-        </is>
-      </c>
-      <c r="B123" s="9" t="inlineStr">
-        <is>
-          <t>색상 코드</t>
-        </is>
-      </c>
-      <c r="C123" s="9" t="inlineStr"/>
-      <c r="D123" s="9" t="inlineStr"/>
-      <c r="E123" s="9" t="inlineStr"/>
-      <c r="F123" s="9" t="inlineStr"/>
+      <c r="A121" s="18" t="inlineStr">
+        <is>
+          <t>미디엄 블루</t>
+        </is>
+      </c>
+      <c r="B121" s="19" t="inlineStr">
+        <is>
+          <t>#42A5F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="16" t="inlineStr">
+        <is>
+          <t>다크 블루</t>
+        </is>
+      </c>
+      <c r="B122" s="17" t="inlineStr">
+        <is>
+          <t>#1E88E5</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="18" t="inlineStr">
+        <is>
+          <t>오렌지 (라인 / YoY)</t>
+        </is>
+      </c>
+      <c r="B123" s="19" t="inlineStr">
+        <is>
+          <t>#FF9800</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="18" customHeight="1">
       <c r="A124" s="16" t="inlineStr">
         <is>
-          <t>주요 바 차트 (라이트 블루)</t>
+          <t>퍼플</t>
         </is>
       </c>
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>#90CAF9</t>
+          <t>#7E57C2</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="18" t="inlineStr">
         <is>
-          <t>미디엄 블루</t>
+          <t>그레이</t>
         </is>
       </c>
       <c r="B125" s="19" t="inlineStr">
         <is>
-          <t>#42A5F5</t>
+          <t>#9E9E9E</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="16" t="inlineStr">
         <is>
-          <t>다크 블루</t>
+          <t>사이드바 배경</t>
         </is>
       </c>
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>#1E88E5</t>
+          <t>#1E2A3A ~ #2C3E50 (그라데이션)</t>
         </is>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="18" t="inlineStr">
         <is>
-          <t>오렌지 (라인 / YoY)</t>
+          <t>현재 페이지 하이라이트</t>
         </is>
       </c>
       <c r="B127" s="19" t="inlineStr">
         <is>
-          <t>#FF9800</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="16" t="inlineStr">
-        <is>
-          <t>퍼플</t>
-        </is>
-      </c>
-      <c r="B128" s="17" t="inlineStr">
-        <is>
-          <t>#7E57C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="18" t="inlineStr">
-        <is>
-          <t>그레이</t>
-        </is>
-      </c>
-      <c r="B129" s="19" t="inlineStr">
-        <is>
-          <t>#9E9E9E</t>
+          <t>#17B9A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="6" customHeight="1"/>
+    <row r="129" ht="22" customHeight="1">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>9. 데이터 흐름 구조</t>
         </is>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="16" t="inlineStr">
-        <is>
-          <t>사이드바 배경</t>
-        </is>
-      </c>
-      <c r="B130" s="17" t="inlineStr">
-        <is>
-          <t>#1E2A3A ~ #2C3E50 (그라데이션)</t>
+      <c r="A130" s="20" t="inlineStr">
+        <is>
+          <t>vf219 (매출총계)          ← 당사 DB 기 수신</t>
         </is>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="18" t="inlineStr">
-        <is>
-          <t>현재 페이지 하이라이트</t>
-        </is>
-      </c>
-      <c r="B131" s="19" t="inlineStr">
-        <is>
-          <t>#17B9A6</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="6" customHeight="1"/>
-    <row r="133" ht="22" customHeight="1">
-      <c r="A133" s="7" t="inlineStr">
-        <is>
-          <t>9. 데이터 흐름 구조</t>
+      <c r="A131" s="20" t="inlineStr">
+        <is>
+          <t>vf599 (영업/마케팅 비용)  ← 당사 DB 기 수신</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      │</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="A133" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      ▼ (지표 산출 로직)</t>
         </is>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>vf219 (매출총계)          ← 당사 DB 기 수신</t>
+          <t>ARPA · 이탈률 · LTV · CAC · LTV:CAC · CAC Payback</t>
         </is>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>vf599 (영업/마케팅 비용)  ← 당사 DB 기 수신</t>
+          <t xml:space="preserve">      │</t>
         </is>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      │</t>
+          <t xml:space="preserve">      ├─▶ Row 2: CAC / LTV / LTV:CAC Ratio 카드</t>
         </is>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ▼ (지표 산출 로직)</t>
+          <t xml:space="preserve">      ├─▶ Row 2: CAC Payback Period 카드</t>
         </is>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>ARPA · 이탈률 · LTV · CAC · LTV:CAC · CAC Payback</t>
+          <t xml:space="preserve">      │</t>
         </is>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      │</t>
+          <t xml:space="preserve">      ▼ (기존 BI 로직 연동)</t>
         </is>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ├─▶ Row 2: CAC / LTV / LTV:CAC Ratio 카드</t>
+          <t>Sales Efficiency · ARPA by ACV/MRR · Revenue on FTE · Rule of 40 · Revenue &amp; Operating Profit · Plan 대비</t>
         </is>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ├─▶ Row 2: CAC Payback Period 카드</t>
+          <t xml:space="preserve">      │</t>
         </is>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      │</t>
+          <t xml:space="preserve">      ▼</t>
         </is>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ▼ (기존 BI 로직 연동)</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="18" customHeight="1">
-      <c r="A144" s="20" t="inlineStr">
-        <is>
-          <t>Sales Efficiency · ARPA by ACV/MRR · Revenue on FTE · Rule of 40 · Revenue &amp; Operating Profit · Plan 대비</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      │</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="18" customHeight="1">
-      <c r="A146" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      ▼</t>
-        </is>
-      </c>
+          <t>효율/수익 대시보드 화면 (Row 1 ~ Row 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="6" customHeight="1"/>
+    <row r="145" ht="22" customHeight="1">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>10. 문의처</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="9" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="C146" s="9" t="inlineStr"/>
+      <c r="D146" s="9" t="inlineStr"/>
+      <c r="E146" s="9" t="inlineStr"/>
+      <c r="F146" s="9" t="inlineStr"/>
     </row>
     <row r="147" ht="18" customHeight="1">
-      <c r="A147" s="20" t="inlineStr">
-        <is>
-          <t>효율/수익 대시보드 화면 (Row 1 ~ Row 6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="6" customHeight="1"/>
-    <row r="149" ht="22" customHeight="1">
-      <c r="A149" s="7" t="inlineStr">
-        <is>
-          <t>10. 문의처</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="20" customHeight="1">
-      <c r="A150" s="9" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B150" s="9" t="inlineStr">
-        <is>
-          <t>내용</t>
-        </is>
-      </c>
-      <c r="C150" s="9" t="inlineStr"/>
-      <c r="D150" s="9" t="inlineStr"/>
-      <c r="E150" s="9" t="inlineStr"/>
-      <c r="F150" s="9" t="inlineStr"/>
-    </row>
-    <row r="151" ht="18" customHeight="1">
-      <c r="A151" s="16" t="inlineStr">
+      <c r="A147" s="16" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="B151" s="16" t="inlineStr">
+      <c r="B147" s="16" t="inlineStr">
         <is>
           <t>[담당자명]</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="18" customHeight="1">
-      <c r="A152" s="18" t="inlineStr">
+    <row r="148" ht="18" customHeight="1">
+      <c r="A148" s="18" t="inlineStr">
         <is>
           <t>부서</t>
         </is>
       </c>
-      <c r="B152" s="18" t="inlineStr">
+      <c r="B148" s="18" t="inlineStr">
         <is>
           <t>솔루션사업부 기획팀</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="18" customHeight="1">
-      <c r="A153" s="16" t="inlineStr">
+    <row r="149" ht="18" customHeight="1">
+      <c r="A149" s="16" t="inlineStr">
         <is>
           <t>연락처</t>
         </is>
       </c>
-      <c r="B153" s="16" t="inlineStr">
+      <c r="B149" s="16" t="inlineStr">
         <is>
           <t>[이메일] / [내선번호]</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="6" customHeight="1"/>
-    <row r="155">
-      <c r="A155" s="21" t="inlineStr">
+    <row r="150" ht="6" customHeight="1"/>
+    <row r="151">
+      <c r="A151" s="21" t="inlineStr">
         <is>
           <t>솔루션사업부 기획팀 · 2026-04-20 · v0.2</t>
         </is>
       </c>
-      <c r="B155" s="22" t="n"/>
-      <c r="C155" s="22" t="n"/>
-      <c r="D155" s="22" t="n"/>
-      <c r="E155" s="22" t="n"/>
-      <c r="F155" s="22" t="n"/>
+      <c r="B151" s="22" t="n"/>
+      <c r="C151" s="22" t="n"/>
+      <c r="D151" s="22" t="n"/>
+      <c r="E151" s="22" t="n"/>
+      <c r="F151" s="22" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="88">
-    <mergeCell ref="B129:F129"/>
+  <mergeCells count="84">
+    <mergeCell ref="B106:F106"/>
     <mergeCell ref="B81:F81"/>
+    <mergeCell ref="A118:F118"/>
     <mergeCell ref="A133:F133"/>
-    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="B122:F122"/>
     <mergeCell ref="B71:F71"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="A144:F144"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A72:F72"/>
     <mergeCell ref="A134:F134"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A107:F107"/>
-    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="A60:F60"/>
     <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A16:F16"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B125:F125"/>
-    <mergeCell ref="B72:F72"/>
-    <mergeCell ref="A149:F149"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="B121:F121"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="B56:F56"/>
     <mergeCell ref="B70:F70"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B105:F105"/>
+    <mergeCell ref="A151:F151"/>
+    <mergeCell ref="B120:F120"/>
     <mergeCell ref="A141:F141"/>
     <mergeCell ref="A135:F135"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="A122:F122"/>
-    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B148:F148"/>
     <mergeCell ref="B82:F82"/>
     <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A114:F114"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A142:F142"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="B153:F153"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="B76:F76"/>
     <mergeCell ref="B85:F85"/>
     <mergeCell ref="B126:F126"/>
     <mergeCell ref="B75:F75"/>
     <mergeCell ref="A137:F137"/>
     <mergeCell ref="B109:F109"/>
-    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="B62:F62"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A145:F145"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A139:F139"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A129:F129"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A131:F131"/>
     <mergeCell ref="A140:F140"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B87:F87"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="B128:F128"/>
-    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A143:F143"/>
-    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="A49:F49"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B110:F110"/>
-    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="A87:F87"/>
     <mergeCell ref="B66:F66"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="B130:F130"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="B151:F151"/>
-    <mergeCell ref="A106:F106"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B77:F77"/>
     <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B61:F61"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A147:F147"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="B69:F69"/>
     <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B112:F112"/>
-    <mergeCell ref="A155:F155"/>
+    <mergeCell ref="A130:F130"/>
     <mergeCell ref="B127:F127"/>
     <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B64:F64"/>
     <mergeCell ref="A138:F138"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="A146:F146"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A132:F132"/>
+    <mergeCell ref="A110:F110"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/efficiency_profit_dev_request.xlsx
+++ b/efficiency_profit_dev_request.xlsx
@@ -877,7 +877,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>vf219</t>
+          <t>l_sap.orderlist.vf219</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>상품 코드 · 연도 기준 컬럼 — 개발팀 확인 필요</t>
+          <t>상품 코드 · 연도 기준 컬럼 — SDSC 확인 필요</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>vf599</t>
+          <t>l_sap.orderlist.vf599</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>상품 코드 · 연도 기준 컬럼 — 개발팀 확인 필요</t>
+          <t>상품 코드 · 연도 기준 컬럼 — SDSC 확인 필요</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>개발팀 확인 필요</t>
+          <t>SDSC 확인 필요</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">

--- a/efficiency_profit_dev_request.xlsx
+++ b/efficiency_profit_dev_request.xlsx
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -712,14 +712,14 @@
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>사업건전성 대시보드의 효율/수익 영역 지표 산출 로직을 드리니, 화면 개발을 요청합니다.</t>
+          <t>사업건전성 대시보드의 효율/수익 영역 지표 산출 로직 개발을 요청합니다.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>원천 데이터(vf219, vf599 등)는 당사 DB에 이미 수신 중이며, Row 1~6 화면은 Tableau로 기 구현되어 있어 본 요청서의 개발 범위에서 제외합니다.</t>
+          <t>원천 데이터(l_sap.orderlist.vf219, vf599)는 당사 DB에 이미 수신 중이며, Row 1~6 화면은 Tableau로 기 구현되어 있어 본 요청서의 개발 범위에서 제외합니다. 신규 지표(LTV·CAC·LTV:CAC·CAC Payback)는 Row 2에 배치 예정입니다.</t>
         </is>
       </c>
     </row>
@@ -855,19 +855,15 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>조회 조건</t>
+          <t>필요 범위</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>히스토리 범위</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
           <t>활용 지표</t>
         </is>
       </c>
+      <c r="F19" s="9" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
@@ -887,19 +883,15 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>상품 코드 · 연도 기준 컬럼 — SDSC 확인 필요</t>
+          <t>2021년 ~ 현재</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>2022년 ~ 현재</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
           <t>LTV · ARPA · 이탈률</t>
         </is>
       </c>
+      <c r="F20" s="10" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
@@ -919,778 +911,696 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>상품 코드 · 연도 기준 컬럼 — SDSC 확인 필요</t>
+          <t>2021년 ~ 현재</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>2022년 ~ 현재</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
           <t>CAC</t>
         </is>
       </c>
+      <c r="F21" s="11" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>Revenue · Operating Profit · Plan · FTE · ARR 등</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>SDSC 확인 필요</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>Row 5 기준: 2023.10 ~ 현재</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>Row 1·3·4·5·6 지표</t>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>※ 2023년 LTV/CAC 산출 시 N-2년(2021년) 데이터까지 필요하므로 원천 데이터 범위는 2021년부터 확보 필요</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>※ vf219는 RC/NRC 데이터 분리가 어려우므로, 실무 적용 시 전체 매출을 Recurring Revenue로 간주하여 사용합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="6" customHeight="1"/>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>4. 마스터 데이터 요청 (화면 필터용)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>화면 상단 상품 드롭다운 필터 구현을 위해 아래 마스터 데이터가 필요합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>내용</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>샘플값</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr"/>
-      <c r="F27" s="9" t="inlineStr"/>
+          <t>※ 상품 구분 컬럼명 / 연도 기준 컬럼명 / 고객 식별 키 컬럼명 — SDSC 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>※ vf219는 RC/NRC 데이터 분리 불가로 전체 매출을 Recurring Revenue로 간주하여 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="6" customHeight="1"/>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>4. 상품 분류 및 지표 산출 가능 여부</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>상품 목록</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>필터 드롭다운에 표시될 상품명 목록 (코드 + 표시명)</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>ZTM · Nexprime SCM · Knox Portal · EMS 등 13개</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr"/>
-      <c r="F28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>상품 그룹핑</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>상품 개별 / 전체(All) 선택 구분</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>Knox (All) = Knox Portal + Knox Meeting + Knox EFSS/Drive</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr"/>
-      <c r="F29" s="11" t="inlineStr"/>
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>※ EMS vs EMS(All) 구분 기준(코드 범위, 포함 기준 등) — SDSC 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>License Type</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Price Type</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>RC/NRC</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>LTV / CAC / LTV:CAC / CAC Payback</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>ZTM</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>EMS 예외 처리</t>
+          <t>Term</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>EMS / EMS(All) 선택 시 LTV:CAC 관련 카드 N/A 표시 처리용 플래그</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>is_ltv_applicable: Y/N</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr"/>
+          <t>RC</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>✅ / ✅ / ✅ / ✅</t>
+        </is>
+      </c>
       <c r="F30" s="10" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>※ 상품 코드 체계 및 마스터 테이블명은 개발팀 확인 후 공유 바랍니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="6" customHeight="1"/>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>5. 상품 분류 및 지표 산출 가능 여부</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>상품</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>License Type</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Price Type</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>RC/NRC</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>LTV / CAC / LTV:CAC / CAC Payback</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr"/>
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>Nexprime SCM</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Term</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>RC</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>✅ / ✅ / ✅ / ✅</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Nexprime SCM Mobile</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Term</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>RC</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>✅ / ✅ / ✅ / ✅</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>Nexprime SCM (All)</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Term</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>RC</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>✅ / ✅ / ✅ / ✅</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Nexprime HCM</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Term</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>RC</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>✅ / ✅ / ✅ / ✅</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>ZTM</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Knox Portal</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>✅ / ✅ / ✅ / ✅</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr"/>
+      <c r="F35" s="11" t="inlineStr"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>Nexprime SCM</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Knox Meeting</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>✅ / ✅ / ✅ / ✅</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr"/>
+      <c r="F36" s="10" t="inlineStr"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>Nexprime SCM Mobile</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>Knox EFSS/Drive</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>✅ / ✅ / ✅ / ✅</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr"/>
+      <c r="F37" s="11" t="inlineStr"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>Nexprime SCM (All)</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Knox (All)</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>✅ / ✅ / ✅ / ✅</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr"/>
+      <c r="F38" s="10" t="inlineStr"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>Nexprime HCM</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>EMM Cloud</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>✅ / ✅ / ✅ / ✅</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr"/>
+      <c r="F39" s="11" t="inlineStr"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>Knox Portal</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>Term</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>Usage</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>RC</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Brity Automation</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Term+Perpetual</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Fixed+One-time</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>RC+Non-RC</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>✅ / ✅ / ✅ / ✅</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr"/>
+      <c r="F40" s="10" t="inlineStr"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>Knox Meeting</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>Term</t>
-        </is>
-      </c>
-      <c r="C41" s="10" t="inlineStr">
-        <is>
-          <t>Usage</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>RC</t>
-        </is>
-      </c>
-      <c r="E41" s="10" t="inlineStr">
-        <is>
-          <t>✅ / ✅ / ✅ / ✅</t>
-        </is>
-      </c>
-      <c r="F41" s="10" t="inlineStr"/>
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>EMS</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Term+Perpetual</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Fixed+One-time</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>RC+Non-RC</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>❌ / ✅ / ❌ / ❌</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>Knox EFSS/Drive</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>Term</t>
-        </is>
-      </c>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>Usage</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="inlineStr">
-        <is>
-          <t>RC</t>
-        </is>
-      </c>
-      <c r="E42" s="11" t="inlineStr">
-        <is>
-          <t>✅ / ✅ / ✅ / ✅</t>
-        </is>
-      </c>
-      <c r="F42" s="11" t="inlineStr"/>
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>EMS (All)</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Term+Perpetual</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Fixed+One-time</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>RC+Non-RC</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>❌ / ✅ / ❌ / ❌</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>Knox (All)</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>Term</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>Usage</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>RC</t>
-        </is>
-      </c>
-      <c r="E43" s="10" t="inlineStr">
-        <is>
-          <t>✅ / ✅ / ✅ / ✅</t>
-        </is>
-      </c>
-      <c r="F43" s="10" t="inlineStr"/>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>EMM Cloud</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>Term</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>Usage</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="inlineStr">
-        <is>
-          <t>RC</t>
-        </is>
-      </c>
-      <c r="E44" s="11" t="inlineStr">
-        <is>
-          <t>✅ / ✅ / ✅ / ✅</t>
-        </is>
-      </c>
-      <c r="F44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>Brity Automation</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>Term+Perpetual</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t>Fixed+One-time</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>RC+Non-RC</t>
-        </is>
-      </c>
-      <c r="E45" s="10" t="inlineStr">
-        <is>
-          <t>✅ / ✅ / ✅ / ✅</t>
-        </is>
-      </c>
-      <c r="F45" s="10" t="inlineStr"/>
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>※ EMS / EMS (All): Recurring 비중 약 9% (라이선스+운영 149억 / 전체 1,572억), 데이터 분리 불가로 LTV · LTV:CAC · CAC Payback 산출 제외. CAC만 산출.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="6" customHeight="1"/>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>5. 지표별 산출 기준</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>EMS</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>Term+Perpetual</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>Fixed+One-time</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="inlineStr">
-        <is>
-          <t>RC+Non-RC</t>
-        </is>
-      </c>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>❌ / ✅ / ❌ / ❌</t>
-        </is>
-      </c>
-      <c r="F46" s="11" t="inlineStr"/>
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>※ 이탈률은 소수 표기 (예: 5% → 0.05). LTV 산식 적용 시 /100 변환 불필요.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>EMS (All)</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>Term+Perpetual</t>
-        </is>
-      </c>
-      <c r="C47" s="10" t="inlineStr">
-        <is>
-          <t>Fixed+One-time</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>RC+Non-RC</t>
-        </is>
-      </c>
-      <c r="E47" s="10" t="inlineStr">
-        <is>
-          <t>❌ / ✅ / ❌ / ❌</t>
-        </is>
-      </c>
-      <c r="F47" s="10" t="inlineStr"/>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>※ EMS / EMS (All): Recurring 비중 약 9% (라이선스+운영 149억 / 전체 1,572억), 데이터 분리 불가로 LTV · LTV:CAC · CAC Payback 산출 제외. CAC만 산출.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="6" customHeight="1"/>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>6. 지표별 산출 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="14" t="inlineStr">
-        <is>
-          <t>6-1. LTV (Customer Lifetime Value)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>※ 상품 구분 컬럼명 / 고객 식별 키 컬럼명 / EMS vs EMS(All) 구분 기준 — SDSC 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>5-1. LTV (Customer Lifetime Value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr"/>
-      <c r="D52" s="9" t="inlineStr"/>
-      <c r="E52" s="9" t="inlineStr"/>
-      <c r="F52" s="9" t="inlineStr"/>
+      <c r="C49" s="9" t="inlineStr"/>
+      <c r="D49" s="9" t="inlineStr"/>
+      <c r="E49" s="9" t="inlineStr"/>
+      <c r="F49" s="9" t="inlineStr"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>산식 (이론)</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>(Recurring 매출에 대한 ARPA ÷ 이탈률) + (연 일회성 매출 ÷ 고객 수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>실무 적용 산식</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>(N년 ARPA ÷ N년 이탈률) + (연 일회성 매출 ÷ 고객 수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>실무 전개</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>(sum(N년 vf219) ÷ 고객 수(N년) ÷ 이탈률(N년)) + (연 일회성 매출 ÷ 고객 수)</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>산식 (이론)</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>(Recurring 매출에 대한 ARPA ÷ 이탈률) + (연 일회성 매출 ÷ 고객 수)</t>
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>RC/NRC 데이터 분리 불가로 vf219 전체를 Recurring으로 간주</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>실무 적용 산식</t>
-        </is>
-      </c>
-      <c r="B54" s="11" t="inlineStr">
-        <is>
-          <t>(sum(vf219) ÷ 고객 수 ÷ 이탈률) + (연 일회성 매출 ÷ 고객 수)</t>
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>적용 상품</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>EMS / EMS(All) 제외 전 상품</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>RC/NRC 데이터 분리 불가로 vf219 전체를 Recurring으로 간주</t>
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>표시 주기</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>Yearly (2023 / 2024 / 2025)</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>적용 상품</t>
-        </is>
-      </c>
-      <c r="B56" s="11" t="inlineStr">
-        <is>
-          <t>EMS / EMS(All) 제외 전 상품</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>표시 주기</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>Yearly (2023 / 2024 / 2025)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B56" s="10" t="inlineStr">
         <is>
           <t>억원</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="14" t="inlineStr">
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ 구성 요소: ARPA / 이탈률</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="9" t="inlineStr">
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr"/>
-      <c r="D60" s="9" t="inlineStr"/>
-      <c r="E60" s="9" t="inlineStr"/>
-      <c r="F60" s="9" t="inlineStr"/>
-    </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>ARPA 산식</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="inlineStr">
-        <is>
-          <t>sum(vf219) ÷ 고객 수  (해당 연도 vf219 ≠ 0인 고객 수 기준)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>이탈률 산식</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="inlineStr">
-        <is>
-          <t>(1 - (N-1년 sum(vf219) ÷ N-2년 sum(vf219))) × 100  ※ N-1년 ≥ N-2년이면 0 → LTV 빈칸</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="14" t="inlineStr">
-        <is>
-          <t>6-2. CAC (Customer Acquisition Cost)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="9" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr"/>
+      <c r="D58" s="9" t="inlineStr"/>
+      <c r="E58" s="9" t="inlineStr"/>
+      <c r="F58" s="9" t="inlineStr"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>N년 ARPA 산식</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>sum(N년 l_sap.orderlist.vf219) ÷ N년 고객 수  (N년 vf219 ≠ 0인 고객 수 기준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>N년 이탈률 산식</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>1 - (N년 sum(vf219) ÷ N-1년 sum(vf219))  ※ 소수 표기. N년 ≥ N-1년이면 0 → LTV 빈칸</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>5-2. CAC (Customer Acquisition Cost)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="9" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B64" s="9" t="inlineStr">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr"/>
-      <c r="D64" s="9" t="inlineStr"/>
-      <c r="E64" s="9" t="inlineStr"/>
-      <c r="F64" s="9" t="inlineStr"/>
+      <c r="C62" s="9" t="inlineStr"/>
+      <c r="D62" s="9" t="inlineStr"/>
+      <c r="E62" s="9" t="inlineStr"/>
+      <c r="F62" s="9" t="inlineStr"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>산식</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>N-2년 sum(l_sap.orderlist.vf599) ÷ N-1년 신규 고객 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>신규 고객 정의</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>N-2년 vf219 = 0 AND N-1년 vf219 ≠ 0</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>산식</t>
+          <t>고객 식별 키</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>N-2년 sum(vf599) ÷ N-1년 신규 고객 수</t>
+          <t>SDSC 확인 필요 (예: customer_id, bp_code 등)</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>신규 고객 정의</t>
+          <t>연도 매핑 예시</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>N-2년 vf219 = 0 AND N-1년 vf219 ≠ 0</t>
+          <t>2023년 CAC = 2021년 vf599 ÷ 2022년 신규 고객 수</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1655,7 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="14" t="inlineStr">
         <is>
-          <t>6-3. LTV:CAC Ratio</t>
+          <t>5-3. LTV:CAC Ratio</t>
         </is>
       </c>
     </row>
@@ -1773,229 +1683,213 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>LTV ÷ CAC</t>
+          <t>N년 LTV ÷ N년 CAC</t>
         </is>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>적용 상품</t>
+          <t>연도 매핑</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>EMS / EMS(All) 제외 전 상품</t>
+          <t>N년 LTV와 N년 CAC(N-2/N-1년 원천 기준)를 동일 표시 연도(N년)로 대응</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>적용 상품</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>배수 (예: 1.6배)</t>
+          <t>EMS / EMS(All) 제외 전 상품</t>
         </is>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>참고 기준</t>
+          <t>단위</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>LTV : CAC = 3 : 1이 적정 수준</t>
+          <t>배수 (예: 1.6배)</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="10" t="inlineStr">
         <is>
+          <t>참고 기준</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>LTV : CAC = 3 : 1이 적정 수준</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
           <t>예외</t>
         </is>
       </c>
-      <c r="B77" s="10" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>LTV 또는 CAC 빈칸이면 빈칸</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="14" t="inlineStr">
-        <is>
-          <t>6-4. CAC Payback Period</t>
-        </is>
-      </c>
-    </row>
     <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="9" t="inlineStr">
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>5-4. CAC Payback Period</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="9" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr">
+      <c r="B80" s="9" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="C79" s="9" t="inlineStr"/>
-      <c r="D79" s="9" t="inlineStr"/>
-      <c r="E79" s="9" t="inlineStr"/>
-      <c r="F79" s="9" t="inlineStr"/>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="10" t="inlineStr">
+      <c r="C80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr"/>
+      <c r="E80" s="9" t="inlineStr"/>
+      <c r="F80" s="9" t="inlineStr"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="10" t="inlineStr">
         <is>
           <t>산식</t>
         </is>
       </c>
-      <c r="B80" s="10" t="inlineStr">
-        <is>
-          <t>(CAC ÷ ARPA) × 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="11" t="inlineStr">
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>(N년 CAC ÷ N년 ARPA) × 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>ARPA 기준</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>N년 ARPA (5-1의 구성 요소 산식과 동일 기준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>적용 상품</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B83" s="10" t="inlineStr">
         <is>
           <t>EMS / EMS(All) 제외 전 상품</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="10" t="inlineStr">
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="B82" s="10" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>개월</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="11" t="inlineStr">
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>참고 기준</t>
         </is>
       </c>
-      <c r="B83" s="11" t="inlineStr">
+      <c r="B85" s="10" t="inlineStr">
         <is>
           <t>B2B SaaS 적정 수준: 12개월 이하</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="10" t="inlineStr">
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t>예외</t>
         </is>
       </c>
-      <c r="B84" s="10" t="inlineStr">
+      <c r="B86" s="11" t="inlineStr">
         <is>
           <t>ARPA = 0 또는 CAC 빈칸이면 빈칸</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="14" t="inlineStr">
-        <is>
-          <t>6-7. Row 1 · 3 · 4 · 5 · 6 지표 (산식 확인 필요)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="15" t="inlineStr">
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="14" t="inlineStr">
+        <is>
+          <t>5-5 ~ 5-9. [참고] Row 1 · 3 · 4 · 5 · 6 지표 (Tableau 기 적용 산식)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="15" t="inlineStr">
         <is>
           <t>※ 아래 지표는 사내 기존 BI 시스템에서 이미 산출 중입니다. 개발팀은 기존 산출 로직 및 데이터 출처(테이블/필드명)를 확인하여 동일 기준으로 적용하되, 확인된 산식을 기획팀에 공유 바랍니다.</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="9" t="inlineStr">
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="9" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B87" s="9" t="inlineStr">
+      <c r="B89" s="9" t="inlineStr">
         <is>
           <t>지표명</t>
         </is>
       </c>
-      <c r="C87" s="9" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="D87" s="9" t="inlineStr"/>
-      <c r="E87" s="9" t="inlineStr"/>
-      <c r="F87" s="9" t="inlineStr"/>
-    </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="10" t="inlineStr">
-        <is>
-          <t>Row 1</t>
-        </is>
-      </c>
-      <c r="B88" s="10" t="inlineStr">
-        <is>
-          <t>Gross Sales Efficiency / Net Sales Efficiency</t>
-        </is>
-      </c>
-      <c r="C88" s="10" t="inlineStr">
-        <is>
-          <t>기존 BI 로직 적용</t>
-        </is>
-      </c>
-      <c r="D88" s="10" t="inlineStr"/>
-      <c r="E88" s="10" t="inlineStr"/>
-      <c r="F88" s="10" t="inlineStr"/>
-    </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="11" t="inlineStr">
-        <is>
-          <t>Row 3</t>
-        </is>
-      </c>
-      <c r="B89" s="11" t="inlineStr">
-        <is>
-          <t>ARPA by ACV / ARPA by MRR (분기별)</t>
-        </is>
-      </c>
-      <c r="C89" s="11" t="inlineStr">
-        <is>
-          <t>기존 BI 로직 적용</t>
-        </is>
-      </c>
-      <c r="D89" s="11" t="inlineStr"/>
-      <c r="E89" s="11" t="inlineStr"/>
-      <c r="F89" s="11" t="inlineStr"/>
+      <c r="D89" s="9" t="inlineStr"/>
+      <c r="E89" s="9" t="inlineStr"/>
+      <c r="F89" s="9" t="inlineStr"/>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>Row 4</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>Revenue on FTE / Rule of 40</t>
+          <t>Gross Sales Efficiency / Net Sales Efficiency</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>기존 BI 로직 적용 — FTE 데이터 출처 확인 필요</t>
+          <t>기존 BI 로직 적용</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr"/>
@@ -2005,12 +1899,12 @@
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>Row 5</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>Revenue &amp; Operating Profit / % Gross Margin &amp; Operating Profit</t>
+          <t>ARPA by ACV / ARPA by MRR (분기별)</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -2025,95 +1919,95 @@
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>Row 6</t>
+          <t>Row 4</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>Revenue vs. Plan / Operating Profit vs. Plan</t>
+          <t>Revenue on FTE / Rule of 40</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>기존 BI 로직 적용 — Plan 데이터 출처 확인 필요</t>
+          <t>기존 BI 로직 적용 — FTE 데이터 출처 확인 필요</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr"/>
       <c r="E92" s="10" t="inlineStr"/>
       <c r="F92" s="10" t="inlineStr"/>
     </row>
-    <row r="93" ht="6" customHeight="1"/>
-    <row r="94" ht="22" customHeight="1">
-      <c r="A94" s="7" t="inlineStr">
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>Row 5</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>Revenue &amp; Operating Profit / % Gross Margin &amp; Operating Profit</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>기존 BI 로직 적용</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr"/>
+      <c r="E93" s="11" t="inlineStr"/>
+      <c r="F93" s="11" t="inlineStr"/>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>Row 6</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>Revenue vs. Plan / Operating Profit vs. Plan</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>기존 BI 로직 적용 — Plan 데이터 출처 확인 필요</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr"/>
+      <c r="E94" s="10" t="inlineStr"/>
+      <c r="F94" s="10" t="inlineStr"/>
+    </row>
+    <row r="95" ht="6" customHeight="1"/>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>7. 예외 처리 기준 (공통)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="9" t="inlineStr">
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="9" t="inlineStr">
         <is>
           <t>조건</t>
         </is>
       </c>
-      <c r="B95" s="9" t="inlineStr">
+      <c r="B97" s="9" t="inlineStr">
         <is>
           <t>처리 방식</t>
         </is>
       </c>
-      <c r="C95" s="9" t="inlineStr">
+      <c r="C97" s="9" t="inlineStr">
         <is>
           <t>영향 지표</t>
         </is>
       </c>
-      <c r="D95" s="9" t="inlineStr"/>
-      <c r="E95" s="9" t="inlineStr"/>
-      <c r="F95" s="9" t="inlineStr"/>
-    </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="10" t="inlineStr">
-        <is>
-          <t>이탈률 = 0</t>
-        </is>
-      </c>
-      <c r="B96" s="10" t="inlineStr">
-        <is>
-          <t>빈칸 표시</t>
-        </is>
-      </c>
-      <c r="C96" s="10" t="inlineStr">
-        <is>
-          <t>LTV · LTV:CAC · CAC Payback</t>
-        </is>
-      </c>
-      <c r="D96" s="10" t="inlineStr"/>
-      <c r="E96" s="10" t="inlineStr"/>
-      <c r="F96" s="10" t="inlineStr"/>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="11" t="inlineStr">
-        <is>
-          <t>신규 고객 수 = 0</t>
-        </is>
-      </c>
-      <c r="B97" s="11" t="inlineStr">
-        <is>
-          <t>빈칸 표시</t>
-        </is>
-      </c>
-      <c r="C97" s="11" t="inlineStr">
-        <is>
-          <t>CAC · LTV:CAC · CAC Payback</t>
-        </is>
-      </c>
-      <c r="D97" s="11" t="inlineStr"/>
-      <c r="E97" s="11" t="inlineStr"/>
-      <c r="F97" s="11" t="inlineStr"/>
+      <c r="D97" s="9" t="inlineStr"/>
+      <c r="E97" s="9" t="inlineStr"/>
+      <c r="F97" s="9" t="inlineStr"/>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>ARPA = 0</t>
+          <t>이탈률 = 0</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
@@ -2123,7 +2017,7 @@
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>CAC Payback</t>
+          <t>LTV · LTV:CAC · CAC Payback</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr"/>
@@ -2133,729 +2027,776 @@
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>EMS / EMS(All) 선택 시</t>
+          <t>신규 고객 수 = 0</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>LTV · LTV:CAC · CAC Payback 카드 N/A 표시</t>
+          <t>빈칸 표시</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Row 2 전체</t>
+          <t>CAC · LTV:CAC · CAC Payback</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr"/>
       <c r="E99" s="11" t="inlineStr"/>
       <c r="F99" s="11" t="inlineStr"/>
     </row>
-    <row r="100" ht="6" customHeight="1"/>
-    <row r="101" ht="22" customHeight="1">
-      <c r="A101" s="7" t="inlineStr">
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>ARPA = 0</t>
+        </is>
+      </c>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>빈칸 표시</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>CAC Payback</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr"/>
+      <c r="E100" s="10" t="inlineStr"/>
+      <c r="F100" s="10" t="inlineStr"/>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>EMS / EMS(All) 선택 시</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>LTV · LTV:CAC · CAC Payback 카드 N/A 표시</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>Row 2 전체</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr"/>
+      <c r="E101" s="11" t="inlineStr"/>
+      <c r="F101" s="11" t="inlineStr"/>
+    </row>
+    <row r="102" ht="6" customHeight="1"/>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="7" t="inlineStr">
         <is>
           <t>8. 화면 개발 스펙</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="14" t="inlineStr">
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="14" t="inlineStr">
         <is>
           <t>8-1. 전체 레이아웃</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="9" t="inlineStr">
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="9" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B103" s="9" t="inlineStr">
+      <c r="B105" s="9" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="C103" s="9" t="inlineStr"/>
-      <c r="D103" s="9" t="inlineStr"/>
-      <c r="E103" s="9" t="inlineStr"/>
-      <c r="F103" s="9" t="inlineStr"/>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="10" t="inlineStr">
-        <is>
-          <t>구성</t>
-        </is>
-      </c>
-      <c r="B104" s="10" t="inlineStr">
-        <is>
-          <t>6 Row × 2 카드 (총 12 카드)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="11" t="inlineStr">
-        <is>
-          <t>상단 필터</t>
-        </is>
-      </c>
-      <c r="B105" s="11" t="inlineStr">
-        <is>
-          <t>상품 드롭다운 (전체 / 상품별 선택) — Section 4 마스터 데이터 기반</t>
-        </is>
-      </c>
+      <c r="C105" s="9" t="inlineStr"/>
+      <c r="D105" s="9" t="inlineStr"/>
+      <c r="E105" s="9" t="inlineStr"/>
+      <c r="F105" s="9" t="inlineStr"/>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>표시 주기</t>
+          <t>구성</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>Yearly 기본 (Row 3·4·5·6은 분기/월별)</t>
+          <t>6 Row × 2 카드 (총 12 카드)</t>
         </is>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>페이지 배경</t>
+          <t>상단 필터</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>#F5F5F5</t>
+          <t>상품 드롭다운 (전체 / 상품별 선택) — Section 4 마스터 데이터 기반</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="10" t="inlineStr">
         <is>
+          <t>표시 주기</t>
+        </is>
+      </c>
+      <c r="B108" s="10" t="inlineStr">
+        <is>
+          <t>Yearly 기본 (Row 3·4·5·6은 분기/월별)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>페이지 배경</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>#F5F5F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
           <t>카드 스타일</t>
         </is>
       </c>
-      <c r="B108" s="10" t="inlineStr">
+      <c r="B110" s="10" t="inlineStr">
         <is>
           <t>border-radius: 8px · box-shadow: 0 2px 8px rgba(0,0,0,0.08)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="14" t="inlineStr">
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="14" t="inlineStr">
         <is>
           <t>8-2. Row별 카드 스펙</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="9" t="inlineStr">
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="9" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="B110" s="9" t="inlineStr">
+      <c r="B112" s="9" t="inlineStr">
         <is>
           <t>카드 (좌)</t>
         </is>
       </c>
-      <c r="C110" s="9" t="inlineStr">
+      <c r="C112" s="9" t="inlineStr">
         <is>
           <t>카드 (우)</t>
         </is>
       </c>
-      <c r="D110" s="9" t="inlineStr">
+      <c r="D112" s="9" t="inlineStr">
         <is>
           <t>차트 타입</t>
         </is>
       </c>
-      <c r="E110" s="9" t="inlineStr">
+      <c r="E112" s="9" t="inlineStr">
         <is>
           <t>X축</t>
         </is>
       </c>
-      <c r="F110" s="9" t="inlineStr">
+      <c r="F112" s="9" t="inlineStr">
         <is>
           <t>단위</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="10" t="inlineStr">
-        <is>
-          <t>Row 1</t>
-        </is>
-      </c>
-      <c r="B111" s="10" t="inlineStr">
-        <is>
-          <t>Gross Sales Efficiency</t>
-        </is>
-      </c>
-      <c r="C111" s="10" t="inlineStr">
-        <is>
-          <t>Net Sales Efficiency</t>
-        </is>
-      </c>
-      <c r="D111" s="10" t="inlineStr">
-        <is>
-          <t>단색 바 차트</t>
-        </is>
-      </c>
-      <c r="E111" s="10" t="inlineStr">
-        <is>
-          <t>2022 / 2023 / 2024</t>
-        </is>
-      </c>
-      <c r="F111" s="10" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="11" t="inlineStr">
-        <is>
-          <t>Row 2</t>
-        </is>
-      </c>
-      <c r="B112" s="11" t="inlineStr">
-        <is>
-          <t>CAC / LTV / LTV:CAC Ratio</t>
-        </is>
-      </c>
-      <c r="C112" s="11" t="inlineStr">
-        <is>
-          <t>CAC Payback Period</t>
-        </is>
-      </c>
-      <c r="D112" s="11" t="inlineStr">
-        <is>
-          <t>콤비네이션(좌) · 라인(우)</t>
-        </is>
-      </c>
-      <c r="E112" s="11" t="inlineStr">
-        <is>
-          <t>2022 / 2023 / 2024</t>
-        </is>
-      </c>
-      <c r="F112" s="11" t="inlineStr">
-        <is>
-          <t>억원 · 배수 / 개월</t>
         </is>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>Row 3</t>
+          <t>Row 1</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>ARPA by ACV</t>
+          <t>Gross Sales Efficiency</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>ARPA by MRR</t>
+          <t>Net Sales Efficiency</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>다중 라인 차트</t>
+          <t>단색 바 차트</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr">
         <is>
-          <t>22.4Q ~ 25.3Q (12분기)</t>
+          <t>2022 / 2023 / 2024</t>
         </is>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>억원 / 천만원</t>
+          <t>%</t>
         </is>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>Row 4</t>
+          <t>Row 2</t>
         </is>
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>Revenue on FTE</t>
+          <t>CAC / LTV / LTV:CAC Ratio</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Rule of 40</t>
+          <t>CAC Payback Period</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>라인(좌) · 다중 라인(우)</t>
+          <t>콤비네이션(좌) · 라인(우)</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>반기 / 22.4Q ~ 25.3Q</t>
+          <t>2022 / 2023 / 2024</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>억원 / %</t>
+          <t>억원 · 배수 / 개월</t>
         </is>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>Row 5</t>
+          <t>Row 3</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>Revenue &amp; Operating Profit</t>
+          <t>ARPA by ACV</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>% Gross Margin &amp; Operating Profit</t>
+          <t>ARPA by MRR</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>콤비네이션 · 다중 라인</t>
+          <t>다중 라인 차트</t>
         </is>
       </c>
       <c r="E115" s="10" t="inlineStr">
         <is>
-          <t>월별 (23.10 ~ 25.10)</t>
+          <t>22.4Q ~ 25.3Q (12분기)</t>
         </is>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>억원 / %</t>
+          <t>억원 / 천만원</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
+          <t>Row 4</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>Revenue on FTE</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>Rule of 40</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>라인(좌) · 다중 라인(우)</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>반기 / 22.4Q ~ 25.3Q</t>
+        </is>
+      </c>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>억원 / %</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>Row 5</t>
+        </is>
+      </c>
+      <c r="B117" s="10" t="inlineStr">
+        <is>
+          <t>Revenue &amp; Operating Profit</t>
+        </is>
+      </c>
+      <c r="C117" s="10" t="inlineStr">
+        <is>
+          <t>% Gross Margin &amp; Operating Profit</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
+        <is>
+          <t>콤비네이션 · 다중 라인</t>
+        </is>
+      </c>
+      <c r="E117" s="10" t="inlineStr">
+        <is>
+          <t>월별 (23.10 ~ 25.10)</t>
+        </is>
+      </c>
+      <c r="F117" s="10" t="inlineStr">
+        <is>
+          <t>억원 / %</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
           <t>Row 6</t>
         </is>
       </c>
-      <c r="B116" s="11" t="inlineStr">
+      <c r="B118" s="11" t="inlineStr">
         <is>
           <t>Revenue vs. Plan</t>
         </is>
       </c>
-      <c r="C116" s="11" t="inlineStr">
+      <c r="C118" s="11" t="inlineStr">
         <is>
           <t>Operating Profit vs. Plan</t>
         </is>
       </c>
-      <c r="D116" s="11" t="inlineStr">
+      <c r="D118" s="11" t="inlineStr">
         <is>
           <t>트리플 바 + 달성률 라인</t>
         </is>
       </c>
-      <c r="E116" s="11" t="inlineStr">
+      <c r="E118" s="11" t="inlineStr">
         <is>
           <t>월별 (1월 ~ 7월)</t>
         </is>
       </c>
-      <c r="F116" s="11" t="inlineStr">
+      <c r="F118" s="11" t="inlineStr">
         <is>
           <t>억원 / %</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="14" t="inlineStr">
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="14" t="inlineStr">
         <is>
           <t>8-3. 색상 시스템</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="9" t="inlineStr">
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="9" t="inlineStr">
         <is>
           <t>요소</t>
         </is>
       </c>
-      <c r="B118" s="9" t="inlineStr">
+      <c r="B120" s="9" t="inlineStr">
         <is>
           <t>색상 코드</t>
         </is>
       </c>
-      <c r="C118" s="9" t="inlineStr"/>
-      <c r="D118" s="9" t="inlineStr"/>
-      <c r="E118" s="9" t="inlineStr"/>
-      <c r="F118" s="9" t="inlineStr"/>
-    </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="16" t="inlineStr">
-        <is>
-          <t>주요 바 차트 (라이트 블루)</t>
-        </is>
-      </c>
-      <c r="B119" s="17" t="inlineStr">
-        <is>
-          <t>#90CAF9</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="18" t="inlineStr">
-        <is>
-          <t>미디엄 블루</t>
-        </is>
-      </c>
-      <c r="B120" s="19" t="inlineStr">
-        <is>
-          <t>#42A5F5</t>
-        </is>
-      </c>
+      <c r="C120" s="9" t="inlineStr"/>
+      <c r="D120" s="9" t="inlineStr"/>
+      <c r="E120" s="9" t="inlineStr"/>
+      <c r="F120" s="9" t="inlineStr"/>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="16" t="inlineStr">
         <is>
-          <t>다크 블루</t>
+          <t>주요 바 차트 (라이트 블루)</t>
         </is>
       </c>
       <c r="B121" s="17" t="inlineStr">
         <is>
-          <t>#1E88E5</t>
+          <t>#90CAF9</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="18" t="inlineStr">
         <is>
-          <t>오렌지 (라인 / YoY)</t>
+          <t>미디엄 블루</t>
         </is>
       </c>
       <c r="B122" s="19" t="inlineStr">
         <is>
-          <t>#FF9800</t>
+          <t>#42A5F5</t>
         </is>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="16" t="inlineStr">
         <is>
-          <t>퍼플</t>
+          <t>다크 블루</t>
         </is>
       </c>
       <c r="B123" s="17" t="inlineStr">
         <is>
-          <t>#7E57C2</t>
+          <t>#1E88E5</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
       <c r="A124" s="18" t="inlineStr">
         <is>
-          <t>그레이</t>
+          <t>오렌지 (라인 / YoY)</t>
         </is>
       </c>
       <c r="B124" s="19" t="inlineStr">
         <is>
-          <t>#9E9E9E</t>
+          <t>#FF9800</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="16" t="inlineStr">
         <is>
-          <t>사이드바 배경</t>
+          <t>퍼플</t>
         </is>
       </c>
       <c r="B125" s="17" t="inlineStr">
         <is>
-          <t>#1E2A3A ~ #2C3E50 (그라데이션)</t>
+          <t>#7E57C2</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="18" t="inlineStr">
         <is>
+          <t>그레이</t>
+        </is>
+      </c>
+      <c r="B126" s="19" t="inlineStr">
+        <is>
+          <t>#9E9E9E</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="16" t="inlineStr">
+        <is>
+          <t>사이드바 배경</t>
+        </is>
+      </c>
+      <c r="B127" s="17" t="inlineStr">
+        <is>
+          <t>#1E2A3A ~ #2C3E50 (그라데이션)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="A128" s="18" t="inlineStr">
+        <is>
           <t>현재 페이지 하이라이트</t>
         </is>
       </c>
-      <c r="B126" s="19" t="inlineStr">
+      <c r="B128" s="19" t="inlineStr">
         <is>
           <t>#17B9A6</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="6" customHeight="1"/>
-    <row r="128" ht="22" customHeight="1">
-      <c r="A128" s="7" t="inlineStr">
+    <row r="129" ht="6" customHeight="1"/>
+    <row r="130" ht="22" customHeight="1">
+      <c r="A130" s="7" t="inlineStr">
         <is>
           <t>9. 데이터 흐름 구조</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="20" t="inlineStr">
-        <is>
-          <t>vf219 (매출총계)          ← 당사 DB 기 수신</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="20" t="inlineStr">
-        <is>
-          <t>vf599 (영업/마케팅 비용)  ← 당사 DB 기 수신</t>
         </is>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      │</t>
+          <t>vf219 (매출총계)          ← 당사 DB 기 수신</t>
         </is>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ▼ (지표 산출 로직)</t>
+          <t>vf599 (영업/마케팅 비용)  ← 당사 DB 기 수신</t>
         </is>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>ARPA · 이탈률 · LTV · CAC · LTV:CAC · CAC Payback</t>
+          <t xml:space="preserve">      │</t>
         </is>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      │</t>
+          <t xml:space="preserve">      ▼ (지표 산출 로직)</t>
         </is>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ├─▶ Row 2: CAC / LTV / LTV:CAC Ratio 카드</t>
+          <t>ARPA · 이탈률 · LTV · CAC · LTV:CAC · CAC Payback</t>
         </is>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ├─▶ Row 2: CAC Payback Period 카드</t>
+          <t xml:space="preserve">      │</t>
         </is>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      │</t>
+          <t xml:space="preserve">      ├─▶ Row 2: CAC / LTV / LTV:CAC Ratio 카드</t>
         </is>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ▼ (기존 BI 로직 연동)</t>
+          <t xml:space="preserve">      ├─▶ Row 2: CAC Payback Period 카드</t>
         </is>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>Sales Efficiency · ARPA by ACV/MRR · Revenue on FTE · Rule of 40 · Revenue &amp; Operating Profit · Plan 대비</t>
+          <t xml:space="preserve">      │</t>
         </is>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      │</t>
+          <t xml:space="preserve">      ▼ (기존 BI 로직 연동)</t>
         </is>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ▼</t>
+          <t>Sales Efficiency · ARPA by ACV/MRR · Revenue on FTE · Rule of 40 · Revenue &amp; Operating Profit · Plan 대비</t>
         </is>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
       <c r="A142" s="20" t="inlineStr">
         <is>
+          <t xml:space="preserve">      │</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="A143" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      ▼</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="A144" s="20" t="inlineStr">
+        <is>
           <t>효율/수익 대시보드 화면 (Row 1 ~ Row 6)</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="6" customHeight="1"/>
-    <row r="144" ht="22" customHeight="1">
-      <c r="A144" s="7" t="inlineStr">
+    <row r="145" ht="6" customHeight="1"/>
+    <row r="146" ht="22" customHeight="1">
+      <c r="A146" s="7" t="inlineStr">
         <is>
           <t>10. 문의처</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="20" customHeight="1">
-      <c r="A145" s="9" t="inlineStr">
+    <row r="147" ht="20" customHeight="1">
+      <c r="A147" s="9" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B145" s="9" t="inlineStr">
+      <c r="B147" s="9" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="C145" s="9" t="inlineStr"/>
-      <c r="D145" s="9" t="inlineStr"/>
-      <c r="E145" s="9" t="inlineStr"/>
-      <c r="F145" s="9" t="inlineStr"/>
-    </row>
-    <row r="146" ht="18" customHeight="1">
-      <c r="A146" s="16" t="inlineStr">
-        <is>
-          <t>담당자</t>
-        </is>
-      </c>
-      <c r="B146" s="16" t="inlineStr">
-        <is>
-          <t>[담당자명]</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="18" customHeight="1">
-      <c r="A147" s="18" t="inlineStr">
-        <is>
-          <t>부서</t>
-        </is>
-      </c>
-      <c r="B147" s="18" t="inlineStr">
-        <is>
-          <t>솔루션사업부 기획팀</t>
-        </is>
-      </c>
+      <c r="C147" s="9" t="inlineStr"/>
+      <c r="D147" s="9" t="inlineStr"/>
+      <c r="E147" s="9" t="inlineStr"/>
+      <c r="F147" s="9" t="inlineStr"/>
     </row>
     <row r="148" ht="18" customHeight="1">
       <c r="A148" s="16" t="inlineStr">
         <is>
+          <t>담당자</t>
+        </is>
+      </c>
+      <c r="B148" s="16" t="inlineStr">
+        <is>
+          <t>[담당자명]</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="A149" s="18" t="inlineStr">
+        <is>
+          <t>부서</t>
+        </is>
+      </c>
+      <c r="B149" s="18" t="inlineStr">
+        <is>
+          <t>솔루션사업부 기획팀</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="A150" s="16" t="inlineStr">
+        <is>
           <t>연락처</t>
         </is>
       </c>
-      <c r="B148" s="16" t="inlineStr">
+      <c r="B150" s="16" t="inlineStr">
         <is>
           <t>[이메일] / [내선번호]</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="6" customHeight="1"/>
-    <row r="150">
-      <c r="A150" s="21" t="inlineStr">
+    <row r="151" ht="6" customHeight="1"/>
+    <row r="152">
+      <c r="A152" s="21" t="inlineStr">
         <is>
           <t>솔루션사업부 기획팀 · 2026-04-20 · v0.2</t>
         </is>
       </c>
-      <c r="B150" s="22" t="n"/>
-      <c r="C150" s="22" t="n"/>
-      <c r="D150" s="22" t="n"/>
-      <c r="E150" s="22" t="n"/>
-      <c r="F150" s="22" t="n"/>
+      <c r="B152" s="22" t="n"/>
+      <c r="C152" s="22" t="n"/>
+      <c r="D152" s="22" t="n"/>
+      <c r="E152" s="22" t="n"/>
+      <c r="F152" s="22" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="84">
+  <mergeCells count="91">
     <mergeCell ref="B106:F106"/>
     <mergeCell ref="B81:F81"/>
     <mergeCell ref="A133:F133"/>
     <mergeCell ref="B122:F122"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A86:F86"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="A150:F150"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="B60:F60"/>
     <mergeCell ref="A144:F144"/>
     <mergeCell ref="A134:F134"/>
     <mergeCell ref="B53:F53"/>
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A152:F152"/>
     <mergeCell ref="B108:F108"/>
     <mergeCell ref="B84:F84"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B125:F125"/>
+    <mergeCell ref="A27:F27"/>
     <mergeCell ref="B121:F121"/>
     <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A101:F101"/>
     <mergeCell ref="B56:F56"/>
     <mergeCell ref="B70:F70"/>
-    <mergeCell ref="B105:F105"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A85:F85"/>
-    <mergeCell ref="B120:F120"/>
     <mergeCell ref="A141:F141"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="B107:F107"/>
     <mergeCell ref="A135:F135"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B57:F57"/>
     <mergeCell ref="B148:F148"/>
     <mergeCell ref="B82:F82"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A9:F9"/>
-    <mergeCell ref="B146:F146"/>
     <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A59:F59"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="B68:F68"/>
     <mergeCell ref="B83:F83"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A142:F142"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A61:F61"/>
     <mergeCell ref="B76:F76"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B126:F126"/>
     <mergeCell ref="B75:F75"/>
     <mergeCell ref="A137:F137"/>
-    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="B109:F109"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B150:F150"/>
     <mergeCell ref="A136:F136"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A139:F139"/>
     <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A129:F129"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A131:F131"/>
     <mergeCell ref="A140:F140"/>
-    <mergeCell ref="A109:F109"/>
-    <mergeCell ref="A63:F63"/>
     <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A117:F117"/>
+    <mergeCell ref="A111:F111"/>
+    <mergeCell ref="B128:F128"/>
+    <mergeCell ref="A143:F143"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="B63:F63"/>
     <mergeCell ref="B123:F123"/>
-    <mergeCell ref="A78:F78"/>
-    <mergeCell ref="A128:F128"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="A87:F87"/>
     <mergeCell ref="B66:F66"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="A104:F104"/>
+    <mergeCell ref="A57:F57"/>
     <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B86:F86"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B61:F61"/>
-    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="A43:F43"/>
     <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B78:F78"/>
     <mergeCell ref="A130:F130"/>
+    <mergeCell ref="B127:F127"/>
     <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B64:F64"/>
     <mergeCell ref="A138:F138"/>
     <mergeCell ref="A132:F132"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="A146:F146"/>
+    <mergeCell ref="A119:F119"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
